--- a/src/__tests__/fixtures/xtb_closed_positions.xlsx
+++ b/src/__tests__/fixtures/xtb_closed_positions.xlsx
@@ -3,7 +3,10 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="CLOSED POSITION HISTORY " sheetId="1" r:id="rId1"/>
+    <sheet name="CLOSED POSITION HISTORY" sheetId="1" r:id="rId1"/>
+    <sheet name="OPEN POSITION 19042026" sheetId="2" r:id="rId2"/>
+    <sheet name="PENDING ORDERS HISTORY " sheetId="3" r:id="rId3"/>
+    <sheet name="CASH OPERATION HISTORY" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -400,10 +403,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:X18"/>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v/>
+      </c>
+      <c r="L1" t="str">
+        <v>History of transactions and operations</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="E4" t="str">
+        <v>Date range</v>
+      </c>
+      <c r="H4" t="str">
+        <v>2024-01-01 - 2025-12-31</v>
+      </c>
+    </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v/>
-      </c>
       <c r="B6" t="str">
         <v/>
       </c>
@@ -414,40 +430,19 @@
         <v/>
       </c>
       <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
         <v>Name and surname</v>
       </c>
-      <c r="H6" t="str">
+      <c r="I6" t="str">
         <v>Account</v>
       </c>
-      <c r="K6" t="str">
+      <c r="L6" t="str">
         <v>Currency</v>
       </c>
-      <c r="N6" t="str">
-        <v/>
-      </c>
-      <c r="O6" t="str">
-        <v/>
-      </c>
-      <c r="P6" t="str">
-        <v/>
-      </c>
-      <c r="Q6" t="str">
-        <v/>
-      </c>
-      <c r="R6" t="str">
-        <v/>
-      </c>
-      <c r="S6" t="str">
-        <v/>
-      </c>
-      <c r="T6" s="1">
-        <v>46131.71853009259</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <v/>
-      </c>
       <c r="B7" t="str">
         <v/>
       </c>
@@ -458,345 +453,130 @@
         <v/>
       </c>
       <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
         <v>Test User</v>
       </c>
-      <c r="H7" t="str">
-        <v>12345678</v>
-      </c>
-      <c r="K7" t="str">
+      <c r="I7" t="str">
+        <v>51723721</v>
+      </c>
+      <c r="L7" t="str">
         <v>PLN</v>
-      </c>
-      <c r="N7" t="str">
-        <v/>
-      </c>
-      <c r="O7" t="str">
-        <v/>
-      </c>
-      <c r="P7" t="str">
-        <v/>
-      </c>
-      <c r="Q7" t="str">
-        <v/>
-      </c>
-      <c r="R7" t="str">
-        <v/>
-      </c>
-      <c r="S7" t="str">
-        <v/>
-      </c>
-      <c r="T7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v/>
-      </c>
-      <c r="B8" t="str">
-        <v/>
-      </c>
-      <c r="C8" t="str">
-        <v/>
-      </c>
-      <c r="D8" t="str">
-        <v/>
-      </c>
-      <c r="E8" t="str">
-        <v>Balance</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Equity</v>
-      </c>
-      <c r="K8" t="str">
-        <v>Margin</v>
-      </c>
-      <c r="N8" t="str">
-        <v>Free margin</v>
-      </c>
-      <c r="Q8" t="str">
-        <v>Margin level</v>
-      </c>
-      <c r="T8" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v/>
-      </c>
-      <c r="B9" t="str">
-        <v/>
-      </c>
-      <c r="C9" t="str">
-        <v/>
-      </c>
-      <c r="D9" t="str">
-        <v/>
-      </c>
-      <c r="E9">
-        <v>1000</v>
-      </c>
-      <c r="H9">
-        <v>1250.5</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>1000</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="T9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v xml:space="preserve">CLOSED POSITION HISTORY </v>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v/>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v/>
-      </c>
-      <c r="M10" t="str">
-        <v/>
-      </c>
-      <c r="N10" t="str">
-        <v/>
-      </c>
-      <c r="O10" t="str">
-        <v/>
-      </c>
-      <c r="P10" t="str">
-        <v/>
-      </c>
-      <c r="Q10" t="str">
-        <v/>
-      </c>
-      <c r="R10" t="str">
-        <v/>
-      </c>
-      <c r="S10" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>01/01/2025 - 31/12/2025</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v/>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v/>
-      </c>
-      <c r="M11" t="str">
-        <v/>
-      </c>
-      <c r="N11" t="str">
-        <v/>
-      </c>
-      <c r="O11" t="str">
-        <v/>
-      </c>
-      <c r="P11" t="str">
-        <v/>
-      </c>
-      <c r="Q11" t="str">
-        <v/>
-      </c>
-      <c r="R11" t="str">
-        <v/>
-      </c>
-      <c r="S11" t="str">
-        <v/>
-      </c>
-      <c r="T11" t="str">
-        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Balance :1000.00 - 0.00</v>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v/>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v/>
-      </c>
-      <c r="M12" t="str">
-        <v/>
-      </c>
-      <c r="N12" t="str">
-        <v/>
-      </c>
-      <c r="O12" t="str">
-        <v/>
-      </c>
-      <c r="P12" t="str">
-        <v/>
-      </c>
-      <c r="Q12" t="str">
-        <v/>
-      </c>
-      <c r="R12" t="str">
-        <v/>
-      </c>
-      <c r="S12" t="str">
-        <v/>
-      </c>
-      <c r="T12" t="str">
-        <v/>
+        <v/>
+      </c>
+      <c r="U12" t="str">
+        <v>CLOSED POSITION HISTORY</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
+        <v/>
+      </c>
+      <c r="B13" t="str">
         <v>Position</v>
       </c>
-      <c r="B13" t="str">
+      <c r="C13" t="str">
         <v>Symbol</v>
       </c>
-      <c r="C13" t="str">
+      <c r="D13" t="str">
         <v>Type</v>
       </c>
-      <c r="D13" t="str">
+      <c r="E13" t="str">
         <v>Volume</v>
       </c>
-      <c r="E13" t="str">
+      <c r="F13" t="str">
         <v>Open time</v>
       </c>
-      <c r="F13" t="str">
+      <c r="G13" t="str">
         <v>Open price</v>
       </c>
-      <c r="G13" t="str">
+      <c r="H13" t="str">
         <v>Close time</v>
       </c>
-      <c r="H13" t="str">
+      <c r="I13" t="str">
         <v>Close price</v>
       </c>
-      <c r="I13" t="str">
+      <c r="J13" t="str">
         <v>Open origin</v>
       </c>
-      <c r="J13" t="str">
+      <c r="K13" t="str">
         <v>Close origin</v>
       </c>
-      <c r="K13" t="str">
+      <c r="L13" t="str">
         <v>Purchase value</v>
       </c>
-      <c r="L13" t="str">
+      <c r="M13" t="str">
         <v>Sale value</v>
       </c>
-      <c r="M13" t="str">
+      <c r="N13" t="str">
         <v>SL</v>
       </c>
-      <c r="N13" t="str">
+      <c r="O13" t="str">
         <v>TP</v>
       </c>
-      <c r="O13" t="str">
+      <c r="P13" t="str">
         <v>Margin</v>
       </c>
-      <c r="P13" t="str">
+      <c r="Q13" t="str">
         <v>Commission</v>
       </c>
-      <c r="Q13" t="str">
+      <c r="R13" t="str">
         <v>Swap</v>
       </c>
-      <c r="R13" t="str">
+      <c r="S13" t="str">
         <v>Rollover</v>
       </c>
-      <c r="S13" t="str">
+      <c r="T13" t="str">
         <v>Gross P/L</v>
       </c>
-      <c r="T13" t="str">
+      <c r="U13" t="str">
         <v>Comment</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
+      <c r="A14" t="str">
+        <v/>
+      </c>
+      <c r="B14">
         <v>1990456723</v>
       </c>
-      <c r="B14" t="str">
+      <c r="C14" t="str">
         <v>IB01.UK</v>
       </c>
-      <c r="C14" t="str">
+      <c r="D14" t="str">
         <v>BUY</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>2</v>
       </c>
-      <c r="E14" s="1">
-        <v>45895.458391203705</v>
-      </c>
-      <c r="F14">
+      <c r="F14" s="1">
+        <v>45895.37505787037</v>
+      </c>
+      <c r="G14">
         <v>117.12</v>
       </c>
-      <c r="G14" s="1">
-        <v>45966.41699074074</v>
-      </c>
-      <c r="H14">
+      <c r="H14" s="1">
+        <v>45966.37532407408</v>
+      </c>
+      <c r="I14">
         <v>118.1</v>
       </c>
-      <c r="I14" t="str">
+      <c r="J14" t="str">
         <v>xStation Mobile iOS</v>
       </c>
-      <c r="J14" t="str">
+      <c r="K14" t="str">
         <v>xStation 5</v>
       </c>
-      <c r="K14">
-        <v>863.9</v>
-      </c>
       <c r="L14">
-        <v>871.15</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
+        <v>234.24</v>
+      </c>
+      <c r="M14">
+        <v>236.2</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -805,157 +585,166 @@
         <v>0</v>
       </c>
       <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
         <v>7.25</v>
       </c>
-      <c r="T14" t="str">
+      <c r="U14" t="str">
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
+      <c r="A15" t="str">
+        <v/>
+      </c>
+      <c r="B15">
         <v>1234567890</v>
       </c>
-      <c r="B15" t="str">
+      <c r="C15" t="str">
         <v>AAPL.US</v>
       </c>
-      <c r="C15" t="str">
+      <c r="D15" t="str">
         <v>BUY</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>10</v>
       </c>
-      <c r="E15" s="1">
+      <c r="F15" s="1">
         <v>45672.416666666664</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>185.5</v>
       </c>
-      <c r="G15" s="1">
-        <v>45828.458333333336</v>
-      </c>
-      <c r="H15">
+      <c r="H15" s="1">
+        <v>45828.604166666664</v>
+      </c>
+      <c r="I15">
         <v>225.1</v>
       </c>
-      <c r="I15" t="str">
+      <c r="J15" t="str">
+        <v>xStation Mobile iOS</v>
+      </c>
+      <c r="K15" t="str">
         <v>xStation 5</v>
       </c>
-      <c r="J15" t="str">
+      <c r="L15">
+        <v>1855</v>
+      </c>
+      <c r="M15">
+        <v>2251</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>396</v>
+      </c>
+      <c r="U15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v/>
+      </c>
+      <c r="B16">
+        <v>9876543210</v>
+      </c>
+      <c r="C16" t="str">
+        <v>BMW.DE</v>
+      </c>
+      <c r="D16" t="str">
+        <v>BUY</v>
+      </c>
+      <c r="E16">
+        <v>5</v>
+      </c>
+      <c r="F16" s="1">
+        <v>45726.333333333336</v>
+      </c>
+      <c r="G16">
+        <v>92.4</v>
+      </c>
+      <c r="H16" s="1">
+        <v>45915.5</v>
+      </c>
+      <c r="I16">
+        <v>98.8</v>
+      </c>
+      <c r="J16" t="str">
+        <v>xStation Mobile iOS</v>
+      </c>
+      <c r="K16" t="str">
         <v>xStation 5</v>
       </c>
-      <c r="K15">
-        <v>1855</v>
-      </c>
-      <c r="L15">
-        <v>2251</v>
-      </c>
-      <c r="P15">
-        <v>0</v>
-      </c>
-      <c r="Q15">
-        <v>0</v>
-      </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <v>396</v>
-      </c>
-      <c r="T15" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16">
-        <v>9876543210</v>
-      </c>
-      <c r="B16" t="str">
-        <v>BMW.DE</v>
-      </c>
-      <c r="C16" t="str">
-        <v>BUY</v>
-      </c>
-      <c r="D16">
-        <v>5</v>
-      </c>
-      <c r="E16" s="1">
-        <v>45726.458333333336</v>
-      </c>
-      <c r="F16">
-        <v>92.4</v>
-      </c>
-      <c r="G16" s="1">
-        <v>45915.666666666664</v>
-      </c>
-      <c r="H16">
-        <v>98.8</v>
-      </c>
-      <c r="I16" t="str">
+      <c r="L16">
+        <v>462</v>
+      </c>
+      <c r="M16">
+        <v>494</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>32</v>
+      </c>
+      <c r="U16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v/>
+      </c>
+      <c r="B17">
+        <v>5555555555</v>
+      </c>
+      <c r="C17" t="str">
+        <v>TSLA.US</v>
+      </c>
+      <c r="D17" t="str">
+        <v>SELL</v>
+      </c>
+      <c r="E17">
+        <v>3</v>
+      </c>
+      <c r="F17" s="1">
+        <v>45301.375</v>
+      </c>
+      <c r="G17">
+        <v>250</v>
+      </c>
+      <c r="H17" s="1">
+        <v>45473.625</v>
+      </c>
+      <c r="I17">
+        <v>220</v>
+      </c>
+      <c r="J17" t="str">
+        <v>xStation Mobile iOS</v>
+      </c>
+      <c r="K17" t="str">
         <v>xStation 5</v>
       </c>
-      <c r="J16" t="str">
-        <v>xStation 5</v>
-      </c>
-      <c r="K16">
-        <v>462</v>
-      </c>
-      <c r="L16">
-        <v>494</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>0</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>32</v>
-      </c>
-      <c r="T16" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17">
-        <v>1111111111</v>
-      </c>
-      <c r="B17" t="str">
-        <v>TSLA.US</v>
-      </c>
-      <c r="C17" t="str">
-        <v>SELL</v>
-      </c>
-      <c r="D17">
-        <v>2</v>
-      </c>
-      <c r="E17" s="1">
-        <v>45689.416666666664</v>
-      </c>
-      <c r="F17">
-        <v>200</v>
-      </c>
-      <c r="G17" s="1">
-        <v>45698.666666666664</v>
-      </c>
-      <c r="H17">
-        <v>180</v>
-      </c>
-      <c r="I17" t="str">
-        <v>xStation 5</v>
-      </c>
-      <c r="J17" t="str">
-        <v>xStation 5</v>
-      </c>
-      <c r="K17">
-        <v>400</v>
-      </c>
       <c r="L17">
-        <v>360</v>
-      </c>
-      <c r="P17">
-        <v>0</v>
+        <v>750</v>
+      </c>
+      <c r="M17">
+        <v>660</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -964,72 +753,24 @@
         <v>0</v>
       </c>
       <c r="S17">
-        <v>40</v>
-      </c>
-      <c r="T17" t="str">
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>-90</v>
+      </c>
+      <c r="U17" t="str">
+        <v>short</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
+        <v/>
+      </c>
+      <c r="B18" t="str">
         <v>Total</v>
       </c>
-      <c r="B18" t="str">
-        <v/>
-      </c>
-      <c r="C18" t="str">
-        <v/>
-      </c>
-      <c r="D18" t="str">
-        <v/>
-      </c>
-      <c r="E18" t="str">
-        <v/>
-      </c>
-      <c r="F18" t="str">
-        <v/>
-      </c>
-      <c r="G18" t="str">
-        <v/>
-      </c>
-      <c r="H18" t="str">
-        <v/>
-      </c>
-      <c r="I18" t="str">
-        <v/>
-      </c>
-      <c r="J18" t="str">
-        <v/>
-      </c>
-      <c r="K18" t="str">
-        <v/>
-      </c>
-      <c r="L18" t="str">
-        <v/>
-      </c>
-      <c r="M18" t="str">
-        <v/>
-      </c>
-      <c r="N18" t="str">
-        <v/>
-      </c>
-      <c r="O18" t="str">
-        <v/>
-      </c>
-      <c r="P18">
-        <v>0</v>
-      </c>
-      <c r="Q18">
-        <v>0</v>
-      </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <v>475.25</v>
-      </c>
-      <c r="T18" t="str">
-        <v/>
+      <c r="T18">
+        <v>335.25</v>
       </c>
     </row>
   </sheetData>
@@ -1037,4 +778,52 @@
     <ignoredError numberStoredAsText="1" sqref="A1:X18"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Open positions</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Pending orders</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Cash operations</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/src/__tests__/fixtures/xtb_closed_positions.xlsx
+++ b/src/__tests__/fixtures/xtb_closed_positions.xlsx
@@ -3,10 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="CLOSED POSITION HISTORY" sheetId="1" r:id="rId1"/>
-    <sheet name="OPEN POSITION 19042026" sheetId="2" r:id="rId2"/>
-    <sheet name="PENDING ORDERS HISTORY " sheetId="3" r:id="rId3"/>
-    <sheet name="CASH OPERATION HISTORY" sheetId="4" r:id="rId4"/>
+    <sheet name="CLOSED POSITION HISTORY " sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -401,25 +398,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X18"/>
+  <dimension ref="A1:U18"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v/>
       </c>
-      <c r="L1" t="str">
+      <c r="B1" t="str">
         <v>History of transactions and operations</v>
       </c>
     </row>
     <row r="4">
-      <c r="E4" t="str">
+      <c r="A4" t="str">
         <v>Date range</v>
       </c>
-      <c r="H4" t="str">
+      <c r="B4" t="str">
         <v>2024-01-01 - 2025-12-31</v>
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="str">
+        <v/>
+      </c>
       <c r="B6" t="str">
         <v/>
       </c>
@@ -430,19 +430,19 @@
         <v/>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>Name and surname</v>
       </c>
       <c r="F6" t="str">
-        <v>Name and surname</v>
-      </c>
-      <c r="I6" t="str">
         <v>Account</v>
       </c>
-      <c r="L6" t="str">
+      <c r="G6" t="str">
         <v>Currency</v>
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="str">
+        <v/>
+      </c>
       <c r="B7" t="str">
         <v/>
       </c>
@@ -453,15 +453,12 @@
         <v/>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v>Test User</v>
       </c>
       <c r="F7" t="str">
-        <v>Test User</v>
-      </c>
-      <c r="I7" t="str">
         <v>51723721</v>
       </c>
-      <c r="L7" t="str">
+      <c r="G7" t="str">
         <v>PLN</v>
       </c>
     </row>
@@ -469,8 +466,8 @@
       <c r="A12" t="str">
         <v/>
       </c>
-      <c r="U12" t="str">
-        <v>CLOSED POSITION HISTORY</v>
+      <c r="B12" t="str">
+        <v xml:space="preserve">CLOSED POSITION HISTORY </v>
       </c>
     </row>
     <row r="13">
@@ -555,13 +552,13 @@
         <v>2</v>
       </c>
       <c r="F14" s="1">
-        <v>45895.37505787037</v>
+        <v>45895.458391203705</v>
       </c>
       <c r="G14">
         <v>117.12</v>
       </c>
       <c r="H14" s="1">
-        <v>45966.37532407408</v>
+        <v>45966.41699074074</v>
       </c>
       <c r="I14">
         <v>118.1</v>
@@ -573,10 +570,10 @@
         <v>xStation 5</v>
       </c>
       <c r="L14">
-        <v>234.24</v>
+        <v>863.9</v>
       </c>
       <c r="M14">
-        <v>236.2</v>
+        <v>871.15</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -590,9 +587,6 @@
       <c r="T14">
         <v>7.25</v>
       </c>
-      <c r="U14" t="str">
-        <v/>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -611,13 +605,13 @@
         <v>10</v>
       </c>
       <c r="F15" s="1">
-        <v>45672.416666666664</v>
+        <v>45672.458333333336</v>
       </c>
       <c r="G15">
         <v>185.5</v>
       </c>
       <c r="H15" s="1">
-        <v>45828.604166666664</v>
+        <v>45828.6875</v>
       </c>
       <c r="I15">
         <v>225.1</v>
@@ -629,10 +623,10 @@
         <v>xStation 5</v>
       </c>
       <c r="L15">
-        <v>1855</v>
+        <v>7500</v>
       </c>
       <c r="M15">
-        <v>2251</v>
+        <v>9000</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -644,10 +638,7 @@
         <v>0</v>
       </c>
       <c r="T15">
-        <v>396</v>
-      </c>
-      <c r="U15" t="str">
-        <v/>
+        <v>1500</v>
       </c>
     </row>
     <row r="16">
@@ -667,13 +658,13 @@
         <v>5</v>
       </c>
       <c r="F16" s="1">
-        <v>45726.333333333336</v>
+        <v>45726.458333333336</v>
       </c>
       <c r="G16">
         <v>92.4</v>
       </c>
       <c r="H16" s="1">
-        <v>45915.5</v>
+        <v>45915.708333333336</v>
       </c>
       <c r="I16">
         <v>98.8</v>
@@ -685,10 +676,10 @@
         <v>xStation 5</v>
       </c>
       <c r="L16">
-        <v>462</v>
+        <v>2000</v>
       </c>
       <c r="M16">
-        <v>494</v>
+        <v>2150</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -700,10 +691,7 @@
         <v>0</v>
       </c>
       <c r="T16">
-        <v>32</v>
-      </c>
-      <c r="U16" t="str">
-        <v/>
+        <v>150</v>
       </c>
     </row>
     <row r="17">
@@ -723,13 +711,13 @@
         <v>3</v>
       </c>
       <c r="F17" s="1">
-        <v>45301.375</v>
+        <v>45301.416666666664</v>
       </c>
       <c r="G17">
         <v>250</v>
       </c>
       <c r="H17" s="1">
-        <v>45473.625</v>
+        <v>45474.708333333336</v>
       </c>
       <c r="I17">
         <v>220</v>
@@ -741,10 +729,10 @@
         <v>xStation 5</v>
       </c>
       <c r="L17">
-        <v>750</v>
+        <v>3000</v>
       </c>
       <c r="M17">
-        <v>660</v>
+        <v>2640</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -769,61 +757,22 @@
       <c r="B18" t="str">
         <v>Total</v>
       </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
       <c r="T18">
-        <v>335.25</v>
+        <v>1617.25</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:X18"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Open positions</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Pending orders</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Cash operations</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:U18"/>
   </ignoredErrors>
 </worksheet>
 </file>